--- a/planilhas/LISTA DE PROCESSO PG + ECO HIBRIDO LADO MENOR.xlsx
+++ b/planilhas/LISTA DE PROCESSO PG + ECO HIBRIDO LADO MENOR.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" state="visible" r:id="rId1"/>
@@ -1460,7 +1460,7 @@
         <v/>
       </c>
       <c r="E39" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F39" s="1" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v/>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F40" s="1" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="E41" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F41" s="1" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v/>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>158</v>
       </c>
       <c r="F42" s="1" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v/>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F43" s="1" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v/>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="F44" s="1" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v/>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F45" s="1" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v/>
       </c>
       <c r="E46" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F46" s="1" t="inlineStr">
         <is>

--- a/planilhas/LISTA DE PROCESSO PG + ECO HIBRIDO LADO MENOR.xlsx
+++ b/planilhas/LISTA DE PROCESSO PG + ECO HIBRIDO LADO MENOR.xlsx
@@ -474,7 +474,7 @@
         <v/>
       </c>
       <c r="E5" t="n">
-        <v>177</v>
+        <v>219</v>
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
         <v/>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
@@ -532,7 +532,7 @@
         <v/>
       </c>
       <c r="E7" t="n">
-        <v>201</v>
+        <v>308</v>
       </c>
       <c r="F7" s="1" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         <v/>
       </c>
       <c r="E8" t="n">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
         <v/>
       </c>
       <c r="E9" t="n">
-        <v>158</v>
+        <v>99</v>
       </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         <v/>
       </c>
       <c r="E10" t="n">
-        <v>366</v>
+        <v>254</v>
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
         <v/>
       </c>
       <c r="E11" t="n">
-        <v>499</v>
+        <v>349</v>
       </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v/>
       </c>
       <c r="E12" t="n">
-        <v>599</v>
+        <v>696</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v/>
       </c>
       <c r="E13" t="n">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="F13" s="1" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v/>
       </c>
       <c r="E14" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v/>
       </c>
       <c r="E15" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F15" s="1" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="E16" t="n">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v/>
       </c>
       <c r="E17" t="n">
-        <v>133</v>
+        <v>545</v>
       </c>
       <c r="F17" s="1" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v/>
       </c>
       <c r="E18" t="n">
-        <v>732</v>
+        <v>567</v>
       </c>
       <c r="F18" s="1" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v/>
       </c>
       <c r="E19" t="n">
-        <v>266</v>
+        <v>68</v>
       </c>
       <c r="F19" s="1" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v/>
       </c>
       <c r="E20" t="n">
-        <v>266</v>
+        <v>1</v>
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v/>
       </c>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>114</v>
       </c>
       <c r="F21" s="1" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v/>
       </c>
       <c r="E22" t="n">
-        <v>69</v>
+        <v>416</v>
       </c>
       <c r="F22" s="1" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v/>
       </c>
       <c r="E23" t="n">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="F23" s="1" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v/>
       </c>
       <c r="E24" t="n">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="F24" s="1" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v/>
       </c>
       <c r="E25" t="n">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="F25" s="1" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v/>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>138</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v/>
       </c>
       <c r="E27" t="n">
-        <v>326</v>
+        <v>467</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v/>
       </c>
       <c r="E28" t="n">
-        <v>272</v>
+        <v>186</v>
       </c>
       <c r="F28" s="1" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v/>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v/>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
